--- a/tool/kintone-resourse-generator/doc/04_受け入れテスト/test-data/run-list/multiple2.xlsx
+++ b/tool/kintone-resourse-generator/doc/04_受け入れテスト/test-data/run-list/multiple2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\04_受け入れテスト\test-data\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE94E6B2-3C5C-46B1-A83B-50624FD3E6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04D4A7C-FCB6-4BC9-ABA1-C7ED526EE355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7FF4BE1-2615-4AD0-9B3E-9441F1BC059F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>スペース識別名</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>TestSpace3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>クラススペース</t>
@@ -439,22 +436,20 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
